--- a/backend/sample-data.xlsx
+++ b/backend/sample-data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,20 +463,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>7395</v>
+        <v>498.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,44 +487,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>7395</v>
+        <v>1065.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2695</v>
+        <v>4604.29</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,44 +535,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>2695</v>
+        <v>6121</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,44 +583,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3900</v>
+        <v>231.55</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,44 +631,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5525</v>
+        <v>109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,44 +679,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>5525</v>
+        <v>416.55</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>2430</v>
+        <v>898.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,44 +727,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>2430</v>
+        <v>1356.24</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>1351</v>
+        <v>1993.25</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -775,44 +775,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>1351</v>
+        <v>567.64</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1328</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -823,44 +823,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>1328</v>
+        <v>2527.43</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>1135</v>
+        <v>1738.05</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -871,44 +871,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>1135</v>
+        <v>819.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>4114</v>
+        <v>997</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -919,44 +919,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>4114</v>
+        <v>62</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C22" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>10560</v>
+        <v>509</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -967,44 +967,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>10560</v>
+        <v>679</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3096</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3096</v>
+        <v>1269.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C26" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>2336</v>
+        <v>5028</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1063,44 +1063,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2336</v>
+        <v>640</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>1460</v>
+        <v>5214.1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1111,44 +1111,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1460</v>
+        <v>1200</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1656</v>
+        <v>132</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1159,44 +1159,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>1656</v>
+        <v>1186.55</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>4213</v>
+        <v>1434.45</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1207,44 +1207,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>4213</v>
+        <v>703.1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1710</v>
+        <v>1460</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1255,44 +1255,44 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>1710</v>
+        <v>631.45</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1968</v>
+        <v>88</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1303,44 +1303,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1968</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4356</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1351,44 +1351,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C39" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4356</v>
+        <v>143.1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>2233</v>
+        <v>3155.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1399,44 +1399,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C41" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>2233</v>
+        <v>3466.15</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
         <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>39</v>
       </c>
       <c r="D42" t="n">
         <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>4221</v>
+        <v>3475.1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1447,44 +1447,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C43" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>4221</v>
+        <v>1528</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1602</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1495,44 +1495,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>1602</v>
+        <v>5331.25</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>11575</v>
+        <v>1651.75</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1543,44 +1543,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>11</v>
+      </c>
+      <c r="C47" t="n">
         <v>18</v>
       </c>
-      <c r="C47" t="n">
-        <v>109</v>
-      </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>11575</v>
+        <v>2063.99</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C48" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3621</v>
+        <v>812.1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1591,44 +1591,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C49" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>3621</v>
+        <v>649</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>3575</v>
+        <v>589.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1639,44 +1639,44 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C51" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>3575</v>
+        <v>891.85</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2415</v>
+        <v>970.35</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1687,44 +1687,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C53" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>2415</v>
+        <v>1751.65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C54" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D54" t="n">
         <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>2664</v>
+        <v>814.6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1735,44 +1735,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C55" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>2664</v>
+        <v>5046.25</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>3168</v>
+        <v>5342.3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1783,44 +1783,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C57" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>3168</v>
+        <v>720.6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>1070</v>
+        <v>1040</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1831,44 +1831,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>1070</v>
+        <v>1020.94</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>2646</v>
+        <v>7400</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1879,44 +1879,44 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>2646</v>
+        <v>167</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1869</v>
+        <v>228</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -1927,44 +1927,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>1869</v>
+        <v>6118.2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>14</v>
       </c>
       <c r="C64" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2988</v>
+        <v>874.15</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -1975,44 +1975,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>2988</v>
+        <v>227.55</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>4708</v>
+        <v>600</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2023,44 +2023,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C67" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>4708</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C68" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>1685</v>
+        <v>2213.05</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2071,44 +2071,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C69" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>1685</v>
+        <v>1691.69</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C70" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>1790</v>
+        <v>1033.3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2119,44 +2119,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C71" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>1790</v>
+        <v>5069</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C72" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>6365</v>
+        <v>599.35</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2167,44 +2167,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C73" t="n">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>6365</v>
+        <v>1058.65</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C74" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3510</v>
+        <v>35.15</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2215,44 +2215,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C75" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>3510</v>
+        <v>3259</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C76" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>8280</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2263,44 +2263,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C77" t="n">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>8280</v>
+        <v>920</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C78" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2311,44 +2311,44 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>1416</v>
+        <v>99.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>3940</v>
+        <v>371.6</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2359,44 +2359,44 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C81" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>3940</v>
+        <v>229.6</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C82" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D82" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>4056</v>
+        <v>1095.25</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2407,44 +2407,44 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C83" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>4056</v>
+        <v>529.05</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C84" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>1065</v>
+        <v>2116.79</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2455,44 +2455,44 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C85" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>1065</v>
+        <v>1028</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>2716</v>
+        <v>232.25</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2503,44 +2503,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>2716</v>
+        <v>2842.75</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C88" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>3393</v>
+        <v>1469.25</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2551,44 +2551,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C89" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>3393</v>
+        <v>998</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>2592</v>
+        <v>333.25</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2599,44 +2599,44 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C91" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2592</v>
+        <v>0</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C92" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1071</v>
+        <v>300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2647,44 +2647,44 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1071</v>
+        <v>676.9400000000001</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -2695,44 +2695,44 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C95" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>2440</v>
+        <v>301.6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C96" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>3200</v>
+        <v>1151.05</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -2743,44 +2743,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C97" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>3200</v>
+        <v>11133.65</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C98" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>7536</v>
+        <v>347.35</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -2791,68 +2791,68 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C99" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>7536</v>
+        <v>0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>4230</v>
+        <v>735</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C101" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D101" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>4230</v>
+        <v>1711.65</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -2863,44 +2863,44 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C102" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D102" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E102" t="n">
-        <v>4900</v>
+        <v>1924.3</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C103" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>4900</v>
+        <v>1188.69</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -2911,44 +2911,44 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C104" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>3341</v>
+        <v>350</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C105" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D105" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>3341</v>
+        <v>2802.75</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -2959,44 +2959,44 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>5550</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C107" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D107" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>5550</v>
+        <v>1159.6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3007,44 +3007,44 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C108" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>2123</v>
+        <v>160</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C109" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>2123</v>
+        <v>0</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3055,44 +3055,44 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>3328</v>
+        <v>898.6</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C111" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>3328</v>
+        <v>336.35</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3103,44 +3103,44 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C112" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E112" t="n">
-        <v>2880</v>
+        <v>2454.45</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C113" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E113" t="n">
-        <v>2880</v>
+        <v>605.55</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3151,44 +3151,44 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C114" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>3421</v>
+        <v>3741.95</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B115" t="n">
+        <v>21</v>
+      </c>
+      <c r="C115" t="n">
+        <v>48</v>
+      </c>
+      <c r="D115" t="n">
         <v>13</v>
       </c>
-      <c r="C115" t="n">
-        <v>49</v>
-      </c>
-      <c r="D115" t="n">
-        <v>11</v>
-      </c>
       <c r="E115" t="n">
-        <v>3421</v>
+        <v>2970.15</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3199,44 +3199,44 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C116" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>2144</v>
+        <v>1026</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C117" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>2144</v>
+        <v>50</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3247,44 +3247,44 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C118" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E118" t="n">
-        <v>1407</v>
+        <v>1881.69</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C119" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D119" t="n">
         <v>7</v>
       </c>
       <c r="E119" t="n">
-        <v>1407</v>
+        <v>2261.55</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3295,44 +3295,44 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C120" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E120" t="n">
-        <v>2210</v>
+        <v>3633.85</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C121" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>2210</v>
+        <v>2308</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3343,44 +3343,44 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C122" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>1299</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C123" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
         <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>1299</v>
+        <v>920</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3391,44 +3391,44 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C124" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>2140</v>
+        <v>33.25</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C125" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>2140</v>
+        <v>1731</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3439,44 +3439,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C126" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D126" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>2674</v>
+        <v>1598</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D127" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E127" t="n">
-        <v>2674</v>
+        <v>1914.2</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3487,44 +3487,44 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C128" t="n">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>6715</v>
+        <v>760</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C129" t="n">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="D129" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E129" t="n">
-        <v>6715</v>
+        <v>3802.05</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3535,44 +3535,44 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C130" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>4972</v>
+        <v>681.6</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C131" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D131" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E131" t="n">
-        <v>4972</v>
+        <v>1671.1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -3583,44 +3583,44 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B132" t="n">
+        <v>21</v>
+      </c>
+      <c r="C132" t="n">
+        <v>33</v>
+      </c>
+      <c r="D132" t="n">
         <v>9</v>
       </c>
-      <c r="C132" t="n">
-        <v>44</v>
-      </c>
-      <c r="D132" t="n">
-        <v>11</v>
-      </c>
       <c r="E132" t="n">
-        <v>4994</v>
+        <v>1964.55</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C133" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>4994</v>
+        <v>657.55</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -3631,44 +3631,44 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D134" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>3938</v>
+        <v>672.25</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C135" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D135" t="n">
         <v>11</v>
       </c>
       <c r="E135" t="n">
-        <v>3938</v>
+        <v>4372.63</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -3679,44 +3679,44 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C136" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E136" t="n">
-        <v>2430</v>
+        <v>2412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C137" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E137" t="n">
-        <v>2430</v>
+        <v>2382.2</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -3727,44 +3727,44 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C138" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>4356</v>
+        <v>460</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
-        <v>4356</v>
+        <v>785.05</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -3775,44 +3775,44 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C140" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" t="n">
-        <v>1263</v>
+        <v>464.15</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>13</v>
       </c>
       <c r="C141" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>1263</v>
+        <v>0</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -3823,44 +3823,44 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>14</v>
       </c>
       <c r="C142" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="D142" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E142" t="n">
-        <v>3056</v>
+        <v>1151.04</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>3056</v>
+        <v>0</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -3871,44 +3871,44 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
-        <v>1647</v>
+        <v>1788.1</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C145" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D145" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E145" t="n">
-        <v>1647</v>
+        <v>602.9400000000001</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -3919,44 +3919,44 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C146" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E146" t="n">
-        <v>965</v>
+        <v>3844</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C147" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E147" t="n">
-        <v>965</v>
+        <v>2837.2</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -3967,44 +3967,44 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C148" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E148" t="n">
-        <v>1624</v>
+        <v>1733.05</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C149" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E149" t="n">
-        <v>1624</v>
+        <v>1013.34</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4015,44 +4015,44 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C150" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="D150" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
-        <v>7056</v>
+        <v>433.25</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C151" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>7056</v>
+        <v>0</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4063,44 +4063,44 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C152" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="D152" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E152" t="n">
-        <v>4785</v>
+        <v>763.25</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C153" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D153" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E153" t="n">
-        <v>4785</v>
+        <v>1009.94</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4111,44 +4111,44 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="D154" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E154" t="n">
-        <v>5504</v>
+        <v>984.8</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>5504</v>
+        <v>1382</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4159,44 +4159,44 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C156" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>1328</v>
+        <v>350.05</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C157" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>1328</v>
+        <v>0</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -4207,44 +4207,44 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C158" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D158" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>2460</v>
+        <v>739</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C159" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>2460</v>
+        <v>422.55</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -4255,44 +4255,44 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C160" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>2496</v>
+        <v>0</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>2496</v>
+        <v>600</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -4303,44 +4303,44 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C162" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>4248</v>
+        <v>670</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C163" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D163" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>4248</v>
+        <v>514</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -4351,44 +4351,44 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C164" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E164" t="n">
-        <v>3632</v>
+        <v>1782.05</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C165" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D165" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>3632</v>
+        <v>1537.94</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -4399,44 +4399,44 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C166" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E166" t="n">
-        <v>1165</v>
+        <v>3022</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C167" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -4447,44 +4447,44 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C168" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>3640</v>
+        <v>145</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C169" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D169" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E169" t="n">
-        <v>3640</v>
+        <v>330</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -4495,44 +4495,44 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C170" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D170" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>2808</v>
+        <v>605</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C171" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E171" t="n">
-        <v>2808</v>
+        <v>1050.55</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -4543,44 +4543,44 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C172" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>2150</v>
+        <v>177.15</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C173" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D173" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>2150</v>
+        <v>164.6</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -4591,44 +4591,44 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C174" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C175" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -4639,44 +4639,44 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C176" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>8275</v>
+        <v>50.05</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C177" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>8275</v>
+        <v>1300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -4687,44 +4687,44 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>3312</v>
+        <v>0</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C179" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>3312</v>
+        <v>0</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -4735,44 +4735,44 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C180" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D180" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E180" t="n">
-        <v>5780</v>
+        <v>969.6</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C181" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
-        <v>5780</v>
+        <v>728.15</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -4783,46 +4783,886 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C182" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D182" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>1588</v>
+        <v>640</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>21</v>
       </c>
       <c r="C183" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>22</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>6</v>
+      </c>
+      <c r="C185" t="n">
+        <v>6</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3</v>
+      </c>
+      <c r="E185" t="n">
+        <v>734.75</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" t="n">
+        <v>18</v>
+      </c>
+      <c r="D186" t="n">
+        <v>6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1104.65</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>8</v>
+      </c>
+      <c r="C187" t="n">
+        <v>47</v>
+      </c>
+      <c r="D187" t="n">
+        <v>15</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2364.4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>9</v>
+      </c>
+      <c r="C188" t="n">
+        <v>31</v>
+      </c>
+      <c r="D188" t="n">
+        <v>9</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1291.55</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>10</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>11</v>
+      </c>
+      <c r="C190" t="n">
+        <v>11</v>
+      </c>
+      <c r="D190" t="n">
+        <v>5</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>12</v>
+      </c>
+      <c r="C191" t="n">
         <v>4</v>
       </c>
-      <c r="E183" t="n">
-        <v>1588</v>
-      </c>
-      <c r="F183" t="inlineStr">
+      <c r="D191" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1192.55</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>13</v>
+      </c>
+      <c r="C192" t="n">
+        <v>7</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1331</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>14</v>
+      </c>
+      <c r="C193" t="n">
+        <v>6</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>15</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1395.05</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>8</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>2516</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>17</v>
+      </c>
+      <c r="C196" t="n">
+        <v>15</v>
+      </c>
+      <c r="D196" t="n">
+        <v>6</v>
+      </c>
+      <c r="E196" t="n">
+        <v>2798.2</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>18</v>
+      </c>
+      <c r="C197" t="n">
+        <v>19</v>
+      </c>
+      <c r="D197" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1045.54</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>19</v>
+      </c>
+      <c r="C198" t="n">
+        <v>42</v>
+      </c>
+      <c r="D198" t="n">
+        <v>11</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1869.3</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>20</v>
+      </c>
+      <c r="C199" t="n">
+        <v>31</v>
+      </c>
+      <c r="D199" t="n">
+        <v>8</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1603.35</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>21</v>
+      </c>
+      <c r="C200" t="n">
+        <v>19</v>
+      </c>
+      <c r="D200" t="n">
+        <v>5</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2185.3</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>22</v>
+      </c>
+      <c r="C201" t="n">
+        <v>4</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>6</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" t="n">
+        <v>324.94</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>7</v>
+      </c>
+      <c r="C203" t="n">
+        <v>49</v>
+      </c>
+      <c r="D203" t="n">
+        <v>16</v>
+      </c>
+      <c r="E203" t="n">
+        <v>4162.15</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>8</v>
+      </c>
+      <c r="C204" t="n">
+        <v>42</v>
+      </c>
+      <c r="D204" t="n">
+        <v>12</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3151.55</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>9</v>
+      </c>
+      <c r="C205" t="n">
+        <v>20</v>
+      </c>
+      <c r="D205" t="n">
+        <v>6</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1494.79</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>10</v>
+      </c>
+      <c r="C206" t="n">
+        <v>8</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" t="n">
+        <v>835.15</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>11</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>12</v>
+      </c>
+      <c r="C208" t="n">
+        <v>6</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>13</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>144.15</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>14</v>
+      </c>
+      <c r="C210" t="n">
+        <v>12</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2838</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>15</v>
+      </c>
+      <c r="C211" t="n">
+        <v>11</v>
+      </c>
+      <c r="D211" t="n">
+        <v>5</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1476.49</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>16</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>184</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>17</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2</v>
+      </c>
+      <c r="E213" t="n">
+        <v>243.25</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>18</v>
+      </c>
+      <c r="C214" t="n">
+        <v>21</v>
+      </c>
+      <c r="D214" t="n">
+        <v>6</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1800.15</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>19</v>
+      </c>
+      <c r="C215" t="n">
+        <v>16</v>
+      </c>
+      <c r="D215" t="n">
+        <v>5</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1573</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>20</v>
+      </c>
+      <c r="C216" t="n">
+        <v>20</v>
+      </c>
+      <c r="D216" t="n">
+        <v>5</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1476.7</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>21</v>
+      </c>
+      <c r="C217" t="n">
+        <v>21</v>
+      </c>
+      <c r="D217" t="n">
+        <v>7</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2801.59</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>22</v>
+      </c>
+      <c r="C218" t="n">
+        <v>7</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1874</v>
+      </c>
+      <c r="F218" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
